--- a/artfynd/A 27733-2026 artfynd.xlsx
+++ b/artfynd/A 27733-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134433783</v>
+        <v>135158838</v>
       </c>
       <c r="B2" t="n">
-        <v>99112</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gullblanka, Vstm</t>
+          <t>Husfallet, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498272</v>
+        <v>498122</v>
       </c>
       <c r="R2" t="n">
-        <v>6620596</v>
+        <v>6620585</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,27 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:33</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,15 +765,1124 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135158853</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Husfallet, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>498196</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6620717</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i död gran</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135158655</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kampaberget, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>498164</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6620577</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färsk bälgrop med fjädrar fr höna</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135158814</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Husfallet, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>498126</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6620578</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fjäder fr höna på sten</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135158604</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Husfallet, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>498215</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6620662</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135158979</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Husfallet, Husfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>498228</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6620682</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hoppade ner i vattnet. Hann ej se art.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135159008</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Husfallet, Husfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>498259</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6620643</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hoppade i vattnet, hann ej se art.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134433783</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gullblanka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>498272</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6620596</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135158988</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Husfallet, Husfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>498231</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6620679</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135159023</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Husfallet, Husfallet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>498275</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6620652</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27733-2026 artfynd.xlsx
+++ b/artfynd/A 27733-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135158838</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135158853</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135158655</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1158,6 +1178,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135158814</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1275,6 +1300,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135158604</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1405,6 +1435,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135158979</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1525,6 +1560,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135159008</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1641,6 +1681,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433783</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1762,6 +1807,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135158988</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1883,8 +1933,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135159023</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27733-2026 artfynd.xlsx
+++ b/artfynd/A 27733-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135158838</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135158853</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>135158655</v>
       </c>
       <c r="B4" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         <v>135158814</v>
       </c>
       <c r="B5" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>135158604</v>
       </c>
       <c r="B6" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>135158979</v>
       </c>
       <c r="B7" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>135159008</v>
       </c>
       <c r="B8" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135158988</v>
       </c>
       <c r="B10" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>135159023</v>
       </c>
       <c r="B11" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27733-2026 artfynd.xlsx
+++ b/artfynd/A 27733-2026 artfynd.xlsx
@@ -1692,7 +1692,7 @@
         <v>135158988</v>
       </c>
       <c r="B10" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>135159023</v>
       </c>
       <c r="B11" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
